--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>96953</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471383.7432972558</v>
+        <v>471384</v>
       </c>
       <c r="R2" t="n">
-        <v>6352213.268056883</v>
+        <v>6352213</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471387.6044458097</v>
+        <v>471388</v>
       </c>
       <c r="R3" t="n">
-        <v>6351913.48026255</v>
+        <v>6351913</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471387.6044458097</v>
+        <v>471388</v>
       </c>
       <c r="R4" t="n">
-        <v>6351913.48026255</v>
+        <v>6351913</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471387.6044458097</v>
+        <v>471388</v>
       </c>
       <c r="R5" t="n">
-        <v>6351913.48026255</v>
+        <v>6351913</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99242</v>
+        <v>99247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99247</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99275</v>
+        <v>99281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99281</v>
+        <v>99288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99292</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106271</v>
+        <v>106276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99307</v>
+        <v>99315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106276</v>
+        <v>106284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247118</v>
       </c>
       <c r="B2" t="n">
-        <v>99315</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74411731</v>
       </c>
       <c r="B3" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573988</v>
       </c>
       <c r="B4" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74767389</v>
       </c>
       <c r="B5" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15408-2025 artfynd.xlsx
+++ b/artfynd/A 15408-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74247118</v>
+        <v>74767389</v>
       </c>
       <c r="B2" t="n">
-        <v>99325</v>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222309</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>21 Granstugan 200 m N, Sm</t>
+          <t>7 Granstugan 150 m OSO(stor lokal), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471384</v>
+        <v>471388</v>
       </c>
       <c r="R2" t="n">
-        <v>6352213</v>
+        <v>6351913</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0e 4728. SOM: Carex ericetorum. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
+          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Platanthera chlorantha. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>50 m SO, gräsbacke</t>
+          <t>Ängsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74411731</v>
+        <v>74573988</v>
       </c>
       <c r="B3" t="n">
-        <v>106294</v>
+        <v>109865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Fraxinus excelsior. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
+          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Leontodon hispidus. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gård</t>
+          <t>300 m O, ängsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,27 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74573988</v>
+        <v>74411731</v>
       </c>
       <c r="B4" t="n">
-        <v>109316</v>
+        <v>106812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220228</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Leontodon hispidus. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
+          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Fraxinus excelsior. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>300 m O, ängsmark</t>
+          <t>Gård</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74767389</v>
+        <v>74247118</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>99781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>222309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>7 Granstugan 150 m OSO(stor lokal), Sm</t>
+          <t>21 Granstugan 200 m N, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471388</v>
+        <v>471384</v>
       </c>
       <c r="R5" t="n">
-        <v>6351913</v>
+        <v>6352213</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E0e 4428. SOM: Platanthera chlorantha. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
+          <t>Smålands flora 2007: KOO: 6E0e 4728. SOM: Carex ericetorum. LEG: Göran Wendt, Signe Karlsson, Margareta Edqvist, Birger Lindgren</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ängsmark</t>
+          <t>50 m SO, gräsbacke</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
